--- a/src/evaluation/data/processed/RES_status_quo_model.xlsx
+++ b/src/evaluation/data/processed/RES_status_quo_model.xlsx
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.812</v>
+        <v>17.468</v>
       </c>
       <c r="C2" t="n">
-        <v>12.66</v>
+        <v>12.08</v>
       </c>
       <c r="D2" t="n">
-        <v>29.056</v>
+        <v>28.85</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8247863247863249</v>
+        <v>0.7722832722832722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3381555153707053</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3968835930339138</v>
+        <v>0.4064773527340999</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.072</v>
+        <v>17.094</v>
       </c>
       <c r="C5" t="n">
         <v>15.68</v>
@@ -556,13 +556,13 @@
         <v>27.038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7118437118437116</v>
+        <v>0.7152014652014653</v>
       </c>
       <c r="F5" t="n">
         <v>0.6112115732368897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7687901008249315</v>
+        <v>0.7873738559023705</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5680568285976172</v>
+        <v>0.5817883126026757</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>0.7992766726943943</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4718148487626035</v>
+        <v>0.4832199014315892</v>
       </c>
     </row>
   </sheetData>
